--- a/artfynd/A 30788-2025 artfynd.xlsx
+++ b/artfynd/A 30788-2025 artfynd.xlsx
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126580782</v>
+        <v>126580614</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>386593</v>
+        <v>386130</v>
       </c>
       <c r="R3" t="n">
-        <v>6842916</v>
+        <v>6842942</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126580526</v>
+        <v>126580713</v>
       </c>
       <c r="B4" t="n">
-        <v>79075</v>
+        <v>78980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,21 +914,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>386181</v>
+        <v>386625</v>
       </c>
       <c r="R4" t="n">
-        <v>6843044</v>
+        <v>6843165</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,12 +968,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126580582</v>
+        <v>126580442</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>79569</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,39 +1011,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tallberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>386189</v>
+        <v>386588</v>
       </c>
       <c r="R5" t="n">
-        <v>6843237</v>
+        <v>6842844</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,17 +1065,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>äldre ringhack (tall)</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126580399</v>
+        <v>126580624</v>
       </c>
       <c r="B6" t="n">
-        <v>79598</v>
+        <v>78739</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,21 +1108,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>386271</v>
+        <v>386537</v>
       </c>
       <c r="R6" t="n">
-        <v>6843047</v>
+        <v>6843050</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1172,12 +1162,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126580861</v>
+        <v>126580688</v>
       </c>
       <c r="B7" t="n">
-        <v>78386</v>
+        <v>78738</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,21 +1205,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1239,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>386252</v>
+        <v>386615</v>
       </c>
       <c r="R7" t="n">
-        <v>6843052</v>
+        <v>6843168</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1269,12 +1259,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126580527</v>
+        <v>126580782</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,39 +1302,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tallberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>386576</v>
+        <v>386593</v>
       </c>
       <c r="R8" t="n">
-        <v>6842921</v>
+        <v>6842916</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1379,11 +1364,6 @@
           <t>2025-07-10</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Tallåga med gammalt bohål</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1408,10 +1388,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126580614</v>
+        <v>126580526</v>
       </c>
       <c r="B9" t="n">
-        <v>78739</v>
+        <v>79075</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,21 +1399,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1423,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>386130</v>
+        <v>386181</v>
       </c>
       <c r="R9" t="n">
-        <v>6842942</v>
+        <v>6843044</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1473,12 +1453,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1505,10 +1485,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126580713</v>
+        <v>126580582</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,34 +1496,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tallberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>386625</v>
+        <v>386189</v>
       </c>
       <c r="R10" t="n">
-        <v>6843165</v>
+        <v>6843237</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1570,12 +1555,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1602,10 +1592,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126580442</v>
+        <v>126580399</v>
       </c>
       <c r="B11" t="n">
-        <v>79569</v>
+        <v>79598</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1613,21 +1603,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1637,10 +1627,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>386588</v>
+        <v>386271</v>
       </c>
       <c r="R11" t="n">
-        <v>6842844</v>
+        <v>6843047</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1667,12 +1657,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1699,10 +1689,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126580624</v>
+        <v>126580861</v>
       </c>
       <c r="B12" t="n">
-        <v>78739</v>
+        <v>78386</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1710,21 +1700,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1734,10 +1724,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>386537</v>
+        <v>386252</v>
       </c>
       <c r="R12" t="n">
-        <v>6843050</v>
+        <v>6843052</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1764,12 +1754,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1796,10 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126580688</v>
+        <v>126580527</v>
       </c>
       <c r="B13" t="n">
-        <v>78738</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1807,34 +1797,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tallberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>386615</v>
+        <v>386576</v>
       </c>
       <c r="R13" t="n">
-        <v>6843168</v>
+        <v>6842921</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1861,12 +1856,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Tallåga med gammalt bohål</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 30788-2025 artfynd.xlsx
+++ b/artfynd/A 30788-2025 artfynd.xlsx
@@ -3256,10 +3256,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126580316</v>
+        <v>126580695</v>
       </c>
       <c r="B28" t="n">
-        <v>79598</v>
+        <v>78738</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3267,21 +3267,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>386655</v>
+        <v>386157</v>
       </c>
       <c r="R28" t="n">
-        <v>6843160</v>
+        <v>6843069</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3321,12 +3321,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3353,10 +3353,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126580706</v>
+        <v>126580478</v>
       </c>
       <c r="B29" t="n">
-        <v>78980</v>
+        <v>79569</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3364,21 +3364,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>386519</v>
+        <v>386259</v>
       </c>
       <c r="R29" t="n">
-        <v>6842906</v>
+        <v>6843196</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3418,17 +3418,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På tall 200+ år</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3455,10 +3450,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126580695</v>
+        <v>126580854</v>
       </c>
       <c r="B30" t="n">
-        <v>78738</v>
+        <v>78386</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3466,21 +3461,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3490,10 +3485,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>386157</v>
+        <v>386400</v>
       </c>
       <c r="R30" t="n">
-        <v>6843069</v>
+        <v>6843176</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3552,7 +3547,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126580478</v>
+        <v>126580472</v>
       </c>
       <c r="B31" t="n">
         <v>79569</v>
@@ -3587,10 +3582,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>386259</v>
+        <v>386503</v>
       </c>
       <c r="R31" t="n">
-        <v>6843196</v>
+        <v>6843147</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3649,10 +3644,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126580854</v>
+        <v>126580694</v>
       </c>
       <c r="B32" t="n">
-        <v>78386</v>
+        <v>78738</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3660,21 +3655,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3684,10 +3679,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>386400</v>
+        <v>386266</v>
       </c>
       <c r="R32" t="n">
-        <v>6843176</v>
+        <v>6843347</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3746,10 +3741,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126580472</v>
+        <v>126580679</v>
       </c>
       <c r="B33" t="n">
-        <v>79569</v>
+        <v>80955</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3757,21 +3752,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>1049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3781,10 +3776,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>386503</v>
+        <v>386455</v>
       </c>
       <c r="R33" t="n">
-        <v>6843147</v>
+        <v>6843318</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3843,10 +3838,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126580694</v>
+        <v>126580316</v>
       </c>
       <c r="B34" t="n">
-        <v>78738</v>
+        <v>79598</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3854,21 +3849,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3878,10 +3873,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>386266</v>
+        <v>386655</v>
       </c>
       <c r="R34" t="n">
-        <v>6843347</v>
+        <v>6843160</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3908,12 +3903,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3940,10 +3935,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126580679</v>
+        <v>126580706</v>
       </c>
       <c r="B35" t="n">
-        <v>80955</v>
+        <v>78980</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3951,21 +3946,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3975,10 +3970,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>386455</v>
+        <v>386519</v>
       </c>
       <c r="R35" t="n">
-        <v>6843318</v>
+        <v>6842906</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4005,12 +4000,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På tall 200+ år</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -22909,7 +22909,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>126580709</v>
+        <v>126580776</v>
       </c>
       <c r="B230" t="n">
         <v>78980</v>
@@ -22944,10 +22944,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>386526</v>
+        <v>386689</v>
       </c>
       <c r="R230" t="n">
-        <v>6842857</v>
+        <v>6842810</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -22974,12 +22974,12 @@
       </c>
       <c r="Y230" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -23006,10 +23006,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>126580726</v>
+        <v>126580363</v>
       </c>
       <c r="B231" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -23017,21 +23017,21 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -23041,10 +23041,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>386537</v>
+        <v>386227</v>
       </c>
       <c r="R231" t="n">
-        <v>6843050</v>
+        <v>6842961</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -23071,12 +23071,12 @@
       </c>
       <c r="Y231" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -23103,10 +23103,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>126580776</v>
+        <v>126580341</v>
       </c>
       <c r="B232" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -23114,21 +23114,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -23138,10 +23138,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>386689</v>
+        <v>386620</v>
       </c>
       <c r="R232" t="n">
-        <v>6842810</v>
+        <v>6842959</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -23200,10 +23200,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>126580363</v>
+        <v>126580457</v>
       </c>
       <c r="B233" t="n">
-        <v>79598</v>
+        <v>79569</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -23211,21 +23211,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -23235,10 +23235,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>386227</v>
+        <v>386599</v>
       </c>
       <c r="R233" t="n">
-        <v>6842961</v>
+        <v>6842970</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -23297,10 +23297,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>126580341</v>
+        <v>126580853</v>
       </c>
       <c r="B234" t="n">
-        <v>79598</v>
+        <v>78386</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -23308,21 +23308,21 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -23332,7 +23332,7 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>386620</v>
+        <v>386232</v>
       </c>
       <c r="R234" t="n">
         <v>6842959</v>
@@ -23394,10 +23394,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>126580457</v>
+        <v>126580396</v>
       </c>
       <c r="B235" t="n">
-        <v>79569</v>
+        <v>79598</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -23405,21 +23405,21 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -23429,10 +23429,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>386599</v>
+        <v>386261</v>
       </c>
       <c r="R235" t="n">
-        <v>6842970</v>
+        <v>6843133</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -23491,10 +23491,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>126580853</v>
+        <v>126580390</v>
       </c>
       <c r="B236" t="n">
-        <v>78386</v>
+        <v>79598</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -23502,21 +23502,21 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -23526,10 +23526,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>386232</v>
+        <v>386211</v>
       </c>
       <c r="R236" t="n">
-        <v>6842959</v>
+        <v>6843191</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -23588,10 +23588,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>126580396</v>
+        <v>126580650</v>
       </c>
       <c r="B237" t="n">
-        <v>79598</v>
+        <v>78739</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -23599,21 +23599,21 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -23623,10 +23623,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>386261</v>
+        <v>386221</v>
       </c>
       <c r="R237" t="n">
-        <v>6843133</v>
+        <v>6842958</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -23685,10 +23685,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>126580390</v>
+        <v>126580709</v>
       </c>
       <c r="B238" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -23696,21 +23696,21 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -23720,10 +23720,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>386211</v>
+        <v>386526</v>
       </c>
       <c r="R238" t="n">
-        <v>6843191</v>
+        <v>6842857</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -23750,12 +23750,12 @@
       </c>
       <c r="Y238" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -23782,10 +23782,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>126580650</v>
+        <v>126580726</v>
       </c>
       <c r="B239" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -23793,21 +23793,21 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -23817,10 +23817,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>386221</v>
+        <v>386537</v>
       </c>
       <c r="R239" t="n">
-        <v>6842958</v>
+        <v>6843050</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -23847,12 +23847,12 @@
       </c>
       <c r="Y239" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AD239" t="b">
